--- a/data/trans_camb/P36BPD07_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P36BPD07_R-Provincia-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-1,83</t>
+          <t>-1,04</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,57</t>
+          <t>-0,43</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>-0,73</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 5,14</t>
+          <t>-7,55; 5,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 8,0</t>
+          <t>-6,4; 5,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 4,79</t>
+          <t>-5,01; 3,25</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-2,18%</t>
+          <t>-1,24%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>-0,49%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-0,26%</t>
+          <t>-0,86%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 6,27</t>
+          <t>-8,69; 7,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 9,54</t>
+          <t>-7,2; 6,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 5,76</t>
+          <t>-5,72; 3,9</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-4,32</t>
+          <t>-3,91</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-6,96</t>
+          <t>-6,86</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-5,68</t>
+          <t>-5,42</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 1,2</t>
+          <t>-9,55; 1,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,37; -2,58</t>
+          <t>-11,13; -2,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,24; -2,33</t>
+          <t>-9,48; -2,01</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-5,15%</t>
+          <t>-4,66%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-7,89%</t>
+          <t>-7,78%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-6,6%</t>
+          <t>-6,29%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 1,46</t>
+          <t>-11,14; 1,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,79; -3,02</t>
+          <t>-12,45; -3,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,57; -2,69</t>
+          <t>-10,75; -2,36</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-14,61</t>
+          <t>-15,5</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-12,18</t>
+          <t>-12,56</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-19,78; -9,48</t>
+          <t>-21,05; -10,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,25; -6,6</t>
+          <t>-13,27; -7,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,19; -9,39</t>
+          <t>-15,47; -9,7</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-15,25%</t>
+          <t>-16,18%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-12,54%</t>
+          <t>-12,94%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-20,57; -10,16</t>
+          <t>-21,66; -11,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,45; -6,84</t>
+          <t>-13,51; -7,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,58; -9,69</t>
+          <t>-15,88; -10,02</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>4,4</t>
+          <t>4,11</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4,47</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,93</t>
+          <t>2,43</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 10,8</t>
+          <t>-3,6; 10,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 10,37</t>
+          <t>-4,57; 6,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 9,6</t>
+          <t>-2,18; 6,67</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 14,14</t>
+          <t>-4,38; 13,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 12,83</t>
+          <t>-5,36; 7,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,1; 12,04</t>
+          <t>-2,59; 8,43</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-4,39</t>
+          <t>-4,89</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,82</t>
+          <t>-1,72</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 3,49</t>
+          <t>-13,18; 2,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 7,93</t>
+          <t>-4,34; 7,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 3,95</t>
+          <t>-6,3; 3,35</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-5,4%</t>
+          <t>-6,02%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-0,98%</t>
+          <t>-2,06%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 4,4</t>
+          <t>-15,76; 3,38</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 9,71</t>
+          <t>-4,86; 8,68</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 4,89</t>
+          <t>-7,18; 4,1</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-1,12</t>
+          <t>-1,01</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1,63</t>
+          <t>1,56</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>0,19</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 4,67</t>
+          <t>-6,62; 5,09</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 6,32</t>
+          <t>-2,58; 6,27</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 3,51</t>
+          <t>-3,41; 3,61</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-1,29%</t>
+          <t>-1,17%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 5,64</t>
+          <t>-7,37; 6,01</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 7,18</t>
+          <t>-2,73; 7,15</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 4,03</t>
+          <t>-3,69; 4,22</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-6,25</t>
+          <t>-4,89</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>4,29</t>
+          <t>-0,64</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,4</t>
+          <t>-2,71</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-11,75; -1,31</t>
+          <t>-9,51; -0,36</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 13,3</t>
+          <t>-4,8; 3,43</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 7,26</t>
+          <t>-5,73; 0,34</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-7,32%</t>
+          <t>-5,73%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>-0,78%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-0,48%</t>
+          <t>-3,24%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-13,54; -1,56</t>
+          <t>-10,96; -0,47</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 16,9</t>
+          <t>-5,7; 4,3</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 8,91</t>
+          <t>-6,8; 0,41</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-27,38</t>
+          <t>-44,02</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-38,54</t>
+          <t>-38,0</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-32,49</t>
+          <t>-40,97</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-45,27; -2,79</t>
+          <t>-48,32; -39,37</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-42,96; -34,71</t>
+          <t>-41,95; -33,69</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-42,03; -12,37</t>
+          <t>-43,99; -37,89</t>
         </is>
       </c>
     </row>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-33,34%</t>
+          <t>-53,61%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-45,24%</t>
+          <t>-44,61%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-38,82%</t>
+          <t>-48,95%</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-54,82; -3,5</t>
+          <t>-57,82; -48,61</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-49,75; -41,13</t>
+          <t>-48,56; -40,32</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-50,08; -14,67</t>
+          <t>-51,99; -45,89</t>
         </is>
       </c>
     </row>
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-10,52</t>
+          <t>-12,92</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-7,79</t>
+          <t>-10,43</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-9,11</t>
+          <t>-11,64</t>
         </is>
       </c>
     </row>
@@ -1339,17 +1339,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-13,29; -4,2</t>
+          <t>-14,96; -10,82</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-10,15; -4,09</t>
+          <t>-12,25; -8,73</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-11,06; -5,98</t>
+          <t>-12,87; -10,23</t>
         </is>
       </c>
     </row>
@@ -1362,17 +1362,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-12,46%</t>
+          <t>-15,31%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-8,98%</t>
+          <t>-12,03%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-10,64%</t>
+          <t>-13,6%</t>
         </is>
       </c>
     </row>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-15,66; -4,98</t>
+          <t>-17,6; -12,91</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-11,64; -4,74</t>
+          <t>-14,01; -10,17</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-12,85; -7,0</t>
+          <t>-15,01; -12,05</t>
         </is>
       </c>
     </row>
